--- a/informes_data/Euroleague/2025-26/playoffs/aggregate_individual/AGG_IND_AS MONACO.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/aggregate_individual/AGG_IND_AS MONACO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T. TARPEY</t>
+          <t>M. JAMES</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7573</v>
+        <v>3.7924</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9537999999999996</v>
+        <v>7.462300000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>3.8035</v>
+        <v>-3.67</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4112999999999998</v>
+        <v>11.7854</v>
       </c>
       <c r="H2" t="n">
-        <v>2.4055</v>
+        <v>3.779100000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.9943</v>
+        <v>8.006499999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>2.0188</v>
+        <v>24.7156</v>
       </c>
       <c r="K2" t="n">
-        <v>3.0001</v>
+        <v>10.7797</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.9814000000000001</v>
+        <v>13.9359</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.6073</v>
+        <v>-12.9302</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5945</v>
+        <v>-7.0005</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.0129</v>
+        <v>-5.9297</v>
       </c>
       <c r="P2" t="n">
-        <v>2.0472</v>
+        <v>-12.511</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.7297</v>
+        <v>-21.8374</v>
       </c>
       <c r="R2" t="n">
-        <v>4.776899999999999</v>
+        <v>9.3264</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2987</v>
+        <v>-3.8163</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6647</v>
+        <v>-4.0667</v>
       </c>
       <c r="U2" t="n">
-        <v>0.634</v>
+        <v>0.2504</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>8.334099999999999</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>8.6508</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.3167000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K. HAYES</t>
+          <t>T. TARPEY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4037</v>
+        <v>2.4316</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7442</v>
+        <v>-0.7254999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.3404</v>
+        <v>3.1571</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.225</v>
+        <v>0.4112999999999998</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.9151000000000002</v>
+        <v>2.4055</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.3098</v>
+        <v>-1.9943</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0122</v>
+        <v>2.0188</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2298</v>
+        <v>3.0001</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7824</v>
+        <v>-0.9814000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>-5.2371</v>
+        <v>-1.6073</v>
       </c>
       <c r="N3" t="n">
-        <v>-3.1449</v>
+        <v>-0.5945</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.0921</v>
+        <v>-1.0129</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2274</v>
+        <v>2.0472</v>
       </c>
       <c r="Q3" t="n">
-        <v>-5.0044</v>
+        <v>-2.7297</v>
       </c>
       <c r="R3" t="n">
-        <v>5.2318</v>
+        <v>4.776899999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8545</v>
+        <v>-0.02690000000000003</v>
       </c>
       <c r="T3" t="n">
-        <v>3.1495</v>
+        <v>-0.01440000000000002</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2951</v>
+        <v>-0.01239999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>1.5468</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>3.587</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.0402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. JAMES</t>
+          <t>K. HAYES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7012</v>
+        <v>-0.5075000000000003</v>
       </c>
       <c r="E4" t="n">
-        <v>5.1007</v>
+        <v>1.8977</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.3996</v>
+        <v>-2.4052</v>
       </c>
       <c r="G4" t="n">
-        <v>11.7854</v>
+        <v>-2.225</v>
       </c>
       <c r="H4" t="n">
-        <v>3.779100000000001</v>
+        <v>-0.9151000000000002</v>
       </c>
       <c r="I4" t="n">
-        <v>8.006499999999999</v>
+        <v>-1.3098</v>
       </c>
       <c r="J4" t="n">
-        <v>24.7156</v>
+        <v>3.0122</v>
       </c>
       <c r="K4" t="n">
-        <v>10.7797</v>
+        <v>2.2298</v>
       </c>
       <c r="L4" t="n">
-        <v>13.9359</v>
+        <v>0.7824</v>
       </c>
       <c r="M4" t="n">
-        <v>-12.9302</v>
+        <v>-5.2371</v>
       </c>
       <c r="N4" t="n">
-        <v>-7.0005</v>
+        <v>-3.1449</v>
       </c>
       <c r="O4" t="n">
-        <v>-5.9297</v>
+        <v>-2.0921</v>
       </c>
       <c r="P4" t="n">
-        <v>-12.511</v>
+        <v>0.2274</v>
       </c>
       <c r="Q4" t="n">
-        <v>-21.8374</v>
+        <v>-5.0044</v>
       </c>
       <c r="R4" t="n">
-        <v>9.3264</v>
+        <v>5.2318</v>
       </c>
       <c r="S4" t="n">
-        <v>-5.9074</v>
+        <v>-0.05680000000000007</v>
       </c>
       <c r="T4" t="n">
-        <v>-6.4282</v>
+        <v>0.3028999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5209</v>
+        <v>-0.3598</v>
       </c>
       <c r="V4" t="n">
-        <v>8.334099999999999</v>
+        <v>1.5468</v>
       </c>
       <c r="W4" t="n">
-        <v>8.6508</v>
+        <v>3.587</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3167000000000001</v>
+        <v>-2.0402</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>-3.1389</v>
+        <v>-3.1317</v>
       </c>
       <c r="E5" t="n">
-        <v>-4.0871</v>
+        <v>-4.4821</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9480999999999999</v>
+        <v>1.3504</v>
       </c>
       <c r="G5" t="n">
         <v>-10.4496</v>
@@ -844,13 +844,13 @@
         <v>6.5967</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5099</v>
+        <v>-0.5029000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.376</v>
+        <v>-1.7713</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8661</v>
+        <v>1.2684</v>
       </c>
       <c r="V5" t="n">
         <v>3.4987</v>
@@ -877,13 +877,13 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.809699999999999</v>
+        <v>-4.878200000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.1818</v>
+        <v>-3.2325</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.6279</v>
+        <v>-1.6458</v>
       </c>
       <c r="G6" t="n">
         <v>-4.9437</v>
@@ -922,13 +922,13 @@
         <v>4.0946</v>
       </c>
       <c r="S6" t="n">
-        <v>1.7</v>
+        <v>0.6315000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8504999999999998</v>
+        <v>-0.2002</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8496</v>
+        <v>0.8316</v>
       </c>
       <c r="V6" t="n">
         <v>-1.2484</v>
@@ -955,13 +955,13 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-5.310099999999999</v>
+        <v>-5.063400000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4149</v>
+        <v>-1.7382</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.8949</v>
+        <v>-3.3252</v>
       </c>
       <c r="G7" t="n">
         <v>-6.033</v>
@@ -1000,13 +1000,13 @@
         <v>8.644</v>
       </c>
       <c r="S7" t="n">
-        <v>-3.3714</v>
+        <v>-3.1248</v>
       </c>
       <c r="T7" t="n">
-        <v>-2.5971</v>
+        <v>-2.9204</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7744</v>
+        <v>-0.2045</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>-12.9685</v>
+        <v>-10.5651</v>
       </c>
       <c r="E8" t="n">
-        <v>-10.6173</v>
+        <v>-9.656499999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.3512</v>
+        <v>-0.9085999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>-7.6645</v>
@@ -1078,13 +1078,13 @@
         <v>7.9615</v>
       </c>
       <c r="S8" t="n">
-        <v>-5.866400000000001</v>
+        <v>-3.463</v>
       </c>
       <c r="T8" t="n">
-        <v>-4.261200000000001</v>
+        <v>-3.3006</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.605</v>
+        <v>-0.1627</v>
       </c>
       <c r="V8" t="n">
         <v>4.2021</v>
@@ -1111,13 +1111,13 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>-18.9169</v>
+        <v>-17.7244</v>
       </c>
       <c r="E9" t="n">
-        <v>-8.7569</v>
+        <v>-7.823</v>
       </c>
       <c r="F9" t="n">
-        <v>-10.16</v>
+        <v>-9.901400000000001</v>
       </c>
       <c r="G9" t="n">
         <v>-12.3231</v>
@@ -1156,13 +1156,13 @@
         <v>2.2747</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.096</v>
+        <v>-1.9036</v>
       </c>
       <c r="T9" t="n">
-        <v>-2.071</v>
+        <v>-1.1371</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.025</v>
+        <v>-0.7664</v>
       </c>
       <c r="V9" t="n">
         <v>-3.2704</v>
@@ -1189,13 +1189,13 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-20.3366</v>
+        <v>-20.2437</v>
       </c>
       <c r="E10" t="n">
-        <v>-11.2809</v>
+        <v>-10.8589</v>
       </c>
       <c r="F10" t="n">
-        <v>-9.0557</v>
+        <v>-9.3849</v>
       </c>
       <c r="G10" t="n">
         <v>-17.396</v>
@@ -1234,13 +1234,13 @@
         <v>5.004300000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.5802</v>
+        <v>-1.4874</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0289</v>
+        <v>-0.607</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5513</v>
+        <v>-0.8805000000000001</v>
       </c>
       <c r="V10" t="n">
         <v>-2.7253</v>
@@ -1267,13 +1267,13 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-24.5372</v>
+        <v>-21.2124</v>
       </c>
       <c r="E11" t="n">
-        <v>-15.7453</v>
+        <v>-13.4107</v>
       </c>
       <c r="F11" t="n">
-        <v>-8.791700000000001</v>
+        <v>-7.8018</v>
       </c>
       <c r="G11" t="n">
         <v>-13.6613</v>
@@ -1312,13 +1312,13 @@
         <v>7.506600000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>-6.3955</v>
+        <v>-3.0707</v>
       </c>
       <c r="T11" t="n">
-        <v>-4.7162</v>
+        <v>-2.3815</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.6792</v>
+        <v>-0.6891</v>
       </c>
       <c r="V11" t="n">
         <v>-0.1582999999999999</v>
@@ -1345,13 +1345,13 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-80.1557</v>
+        <v>-77.1024</v>
       </c>
       <c r="E12" t="n">
-        <v>-43.2855</v>
+        <v>-42.5674</v>
       </c>
       <c r="F12" t="n">
-        <v>-36.8698</v>
+        <v>-34.5354</v>
       </c>
       <c r="G12" t="n">
         <v>-62.4995</v>
@@ -1390,13 +1390,13 @@
         <v>61.4175</v>
       </c>
       <c r="S12" t="n">
-        <v>-19.8736</v>
+        <v>-16.8209</v>
       </c>
       <c r="T12" t="n">
-        <v>-16.8139</v>
+        <v>-16.0963</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.0594</v>
+        <v>-0.725</v>
       </c>
       <c r="V12" t="n">
         <v>10.1793</v>
